--- a/csv/model/DCC/formula_DCC_SK.xlsx
+++ b/csv/model/DCC/formula_DCC_SK.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="32175" yWindow="990" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M131" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M155" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M175" t="n">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M179" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M183" t="n">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M187" t="n">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M191" t="n">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M195" t="n">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M199" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M203" t="n">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15169,7 +15169,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -16261,7 +16261,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -16441,7 +16441,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18526,7 +18526,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -18658,7 +18658,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -19867,7 +19867,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20440,7 +20440,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21417,7 +21417,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -22591,7 +22591,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -22803,7 +22803,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -22894,7 +22894,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23494,7 +23494,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -23882,7 +23882,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24143,7 +24143,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24270,7 +24270,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -24743,7 +24743,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -24834,7 +24834,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25131,7 +25131,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -25907,7 +25907,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -25998,7 +25998,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26471,7 +26471,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26598,7 +26598,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27550,7 +27550,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -28023,7 +28023,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -28150,7 +28150,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -28326,7 +28326,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -28411,7 +28411,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">

--- a/csv/model/DCC/formula_DCC_SK.xlsx
+++ b/csv/model/DCC/formula_DCC_SK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\dev\cims-models\csv\model\DCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\test\cims-models\csv\model\DCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43489D6-120C-4520-AAFF-7BAB01B8A3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79E4C59F-AC0A-45D9-9E45-5C03BE599F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E990FF79-6319-420C-B6E6-9CE496F53D0B}"/>
+    <workbookView xWindow="32505" yWindow="2025" windowWidth="38700" windowHeight="15285" xr2:uid="{32790A30-0E56-492C-AA38-452543A0031F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -952,16 +952,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A9595A-8982-41A4-9054-ACE050DAC402}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80DB2FA1-5B07-4287-8DCB-1A051E0D5B79}">
   <dimension ref="A1:X458"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>17.009699999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>6840</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1805,50 +1805,50 @@
         <v>54</v>
       </c>
       <c r="M16">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W16">
         <f t="shared" ca="1" si="0"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1943,50 +1943,50 @@
         <v>54</v>
       </c>
       <c r="M18">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W18">
         <f t="shared" ca="1" si="0"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2711,50 +2711,50 @@
         <v>54</v>
       </c>
       <c r="M31">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W31">
         <f t="shared" ca="1" si="3"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -2849,50 +2849,50 @@
         <v>54</v>
       </c>
       <c r="M33">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W33">
         <f t="shared" ca="1" si="3"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>48</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>48</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>48</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>48</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>66</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -3617,50 +3617,50 @@
         <v>54</v>
       </c>
       <c r="M46">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="V46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="W46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>66</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -3755,50 +3755,50 @@
         <v>54</v>
       </c>
       <c r="M48">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="R48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="T48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="U48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W48">
         <f t="shared" ca="1" si="6"/>
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>66</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>66</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>66</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>68</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>70</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -4799,7 +4799,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -4937,7 +4937,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>54000000</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>74</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>74</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -5637,7 +5637,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>78</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>78</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>80</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>80</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>80</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>80</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>80</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>82</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>82</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>82</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>7668000</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>82</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>87</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>87</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>87</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>87</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>87</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>87</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>87</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>87</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>87</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>87</v>
       </c>
@@ -7158,7 +7158,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>87</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>87</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>87</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>87</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>87</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>87</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>87</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>87</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>87</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>87</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>87</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>87</v>
       </c>
@@ -7981,7 +7981,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>87</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>87</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>87</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>87</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>87</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>87</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>87</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>87</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>87</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>87</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>125000000</v>
       </c>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>87</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>87</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>87</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>87</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>87</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>87</v>
       </c>
@@ -8968,7 +8968,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>87</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>87</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>87</v>
       </c>
@@ -9132,7 +9132,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>87</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>87</v>
       </c>
@@ -9274,7 +9274,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>104</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>104</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>104</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>104</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>200000000</v>
       </c>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>104</v>
       </c>
@@ -9580,7 +9580,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>108</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>108</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>108</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>108</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>108</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>109</v>
       </c>
@@ -9909,7 +9909,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>109</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>109</v>
       </c>
@@ -10047,7 +10047,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>109</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>109</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>115</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>115</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>115</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>115</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>116</v>
       </c>
@@ -10514,7 +10514,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>116</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>116</v>
       </c>
@@ -10652,7 +10652,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>116</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>2861100</v>
       </c>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>116</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>118</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>118</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>124</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>124</v>
       </c>
@@ -10895,7 +10895,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>125</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>125</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>126</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>126</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>126</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>128</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>128</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>128</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>129</v>
       </c>
@@ -11129,7 +11129,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>129</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>129</v>
       </c>
@@ -11181,7 +11181,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>130</v>
       </c>
@@ -11207,7 +11207,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>130</v>
       </c>
@@ -11233,7 +11233,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>131</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>131</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>132</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>132</v>
       </c>
@@ -11337,7 +11337,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>133</v>
       </c>
@@ -11363,7 +11363,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>133</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>134</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>134</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>135</v>
       </c>
@@ -11467,7 +11467,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>135</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>118</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>118</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>124</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>124</v>
       </c>
@@ -11717,7 +11717,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>125</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>125</v>
       </c>
@@ -11829,7 +11829,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>126</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>126</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>126</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>128</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>128</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>128</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>129</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>129</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>129</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>130</v>
       </c>
@@ -12389,7 +12389,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>130</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>131</v>
       </c>
@@ -12501,7 +12501,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>131</v>
       </c>
@@ -12557,7 +12557,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>132</v>
       </c>
@@ -12613,7 +12613,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>132</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>133</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>133</v>
       </c>
@@ -12781,7 +12781,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>134</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>134</v>
       </c>
@@ -12893,7 +12893,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>135</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>135</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>118</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>118</v>
       </c>
@@ -13117,7 +13117,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>124</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>124</v>
       </c>
@@ -13229,7 +13229,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>125</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>125</v>
       </c>
@@ -13341,7 +13341,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>126</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>126</v>
       </c>
@@ -13453,7 +13453,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>126</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>128</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>128</v>
       </c>
@@ -13621,7 +13621,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>128</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>129</v>
       </c>
@@ -13733,7 +13733,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>129</v>
       </c>
@@ -13789,7 +13789,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>129</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>130</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>130</v>
       </c>
@@ -13957,7 +13957,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>131</v>
       </c>
@@ -14013,7 +14013,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>131</v>
       </c>
@@ -14069,7 +14069,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>132</v>
       </c>
@@ -14125,7 +14125,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>132</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>133</v>
       </c>
@@ -14237,7 +14237,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>133</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>134</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>134</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>135</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>135</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>118</v>
       </c>
@@ -14573,7 +14573,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>118</v>
       </c>
@@ -14629,7 +14629,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>124</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>124</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>125</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>125</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>126</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>126</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>126</v>
       </c>
@@ -15021,7 +15021,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>128</v>
       </c>
@@ -15077,7 +15077,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>128</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>128</v>
       </c>
@@ -15189,7 +15189,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>129</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>129</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>129</v>
       </c>
@@ -15357,7 +15357,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>130</v>
       </c>
@@ -15413,7 +15413,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>130</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>131</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>131</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>132</v>
       </c>
@@ -15637,7 +15637,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>132</v>
       </c>
@@ -15693,7 +15693,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>133</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>133</v>
       </c>
@@ -15805,7 +15805,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>134</v>
       </c>
@@ -15861,7 +15861,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>134</v>
       </c>
@@ -15917,7 +15917,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>135</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>135</v>
       </c>
@@ -16029,7 +16029,7 @@
         <v>27120000</v>
       </c>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>118</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>118</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>124</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>124</v>
       </c>
@@ -16253,7 +16253,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>125</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>125</v>
       </c>
@@ -16365,7 +16365,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>126</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>126</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>126</v>
       </c>
@@ -16533,7 +16533,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>128</v>
       </c>
@@ -16589,7 +16589,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>128</v>
       </c>
@@ -16645,7 +16645,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>128</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>129</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>129</v>
       </c>
@@ -16813,7 +16813,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>129</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>130</v>
       </c>
@@ -16925,7 +16925,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>130</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="289" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>131</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="290" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>131</v>
       </c>
@@ -17093,7 +17093,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="291" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>132</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="292" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>132</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="293" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>133</v>
       </c>
@@ -17261,7 +17261,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="294" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>133</v>
       </c>
@@ -17317,7 +17317,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="295" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>134</v>
       </c>
@@ -17373,7 +17373,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="296" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>134</v>
       </c>
@@ -17429,7 +17429,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="297" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>135</v>
       </c>
@@ -17485,7 +17485,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="298" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>135</v>
       </c>
@@ -17541,7 +17541,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="299" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>27</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="300" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>27</v>
       </c>
@@ -17639,7 +17639,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="301" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>27</v>
       </c>
@@ -17711,7 +17711,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="302" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>27</v>
       </c>
@@ -17783,7 +17783,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="303" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>27</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="304" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>27</v>
       </c>
@@ -17884,7 +17884,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="305" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>27</v>
       </c>
@@ -17956,7 +17956,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="306" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>27</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="307" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>27</v>
       </c>
@@ -18101,7 +18101,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="308" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>27</v>
       </c>
@@ -18173,7 +18173,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="309" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>27</v>
       </c>
@@ -18199,7 +18199,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="310" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>27</v>
       </c>
@@ -18271,7 +18271,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="311" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>27</v>
       </c>
@@ -18343,7 +18343,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="312" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>27</v>
       </c>
@@ -18416,7 +18416,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="313" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>27</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="314" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>29</v>
       </c>
@@ -18514,7 +18514,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="315" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>29</v>
       </c>
@@ -18583,7 +18583,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="316" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>29</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="317" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>29</v>
       </c>
@@ -18725,7 +18725,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="318" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>29</v>
       </c>
@@ -18794,7 +18794,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="319" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>29</v>
       </c>
@@ -18820,7 +18820,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="320" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>29</v>
       </c>
@@ -18889,7 +18889,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="321" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>29</v>
       </c>
@@ -18958,7 +18958,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>29</v>
       </c>
@@ -19031,7 +19031,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="323" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>29</v>
       </c>
@@ -19100,7 +19100,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="324" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>21</v>
       </c>
@@ -19129,7 +19129,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>21</v>
       </c>
@@ -19201,7 +19201,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>21</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="327" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>21</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="328" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>21</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="329" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>21</v>
       </c>
@@ -19444,7 +19444,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="330" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>21</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="331" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>21</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="332" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>21</v>
       </c>
@@ -19661,7 +19661,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="333" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>21</v>
       </c>
@@ -19733,7 +19733,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="334" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>21</v>
       </c>
@@ -19759,7 +19759,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="335" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>21</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="336" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>21</v>
       </c>
@@ -19903,7 +19903,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="337" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>21</v>
       </c>
@@ -19976,7 +19976,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="338" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>21</v>
       </c>
@@ -20048,7 +20048,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="339" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>21</v>
       </c>
@@ -20074,7 +20074,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="340" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>21</v>
       </c>
@@ -20146,7 +20146,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="341" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>21</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="342" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>21</v>
       </c>
@@ -20291,7 +20291,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="343" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>21</v>
       </c>
@@ -20363,7 +20363,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="344" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>154</v>
       </c>
@@ -20389,7 +20389,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="345" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>154</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="346" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>154</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="347" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>154</v>
       </c>
@@ -20603,7 +20603,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="348" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>154</v>
       </c>
@@ -20675,7 +20675,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="349" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>154</v>
       </c>
@@ -20701,7 +20701,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="350" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>154</v>
       </c>
@@ -20770,7 +20770,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="351" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>154</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="352" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>154</v>
       </c>
@@ -20915,7 +20915,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="353" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>154</v>
       </c>
@@ -20987,7 +20987,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="354" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>154</v>
       </c>
@@ -21013,7 +21013,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="355" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>154</v>
       </c>
@@ -21082,7 +21082,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="356" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>154</v>
       </c>
@@ -21154,7 +21154,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="357" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>154</v>
       </c>
@@ -21227,7 +21227,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="358" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>154</v>
       </c>
@@ -21299,7 +21299,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="359" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>154</v>
       </c>
@@ -21325,7 +21325,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="360" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>154</v>
       </c>
@@ -21394,7 +21394,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="361" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>154</v>
       </c>
@@ -21466,7 +21466,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="362" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>154</v>
       </c>
@@ -21539,7 +21539,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="363" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>154</v>
       </c>
@@ -21611,7 +21611,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="364" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>154</v>
       </c>
@@ -21637,7 +21637,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="365" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>154</v>
       </c>
@@ -21706,7 +21706,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="366" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>154</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="367" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>154</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="368" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>154</v>
       </c>
@@ -21923,7 +21923,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="369" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>31</v>
       </c>
@@ -21949,7 +21949,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="370" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>31</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="371" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>31</v>
       </c>
@@ -22087,7 +22087,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="372" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>31</v>
       </c>
@@ -22160,7 +22160,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="373" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>31</v>
       </c>
@@ -22229,7 +22229,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="374" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>31</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="375" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>31</v>
       </c>
@@ -22324,7 +22324,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="376" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>31</v>
       </c>
@@ -22393,7 +22393,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="377" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>31</v>
       </c>
@@ -22466,7 +22466,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="378" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>31</v>
       </c>
@@ -22535,7 +22535,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="379" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>31</v>
       </c>
@@ -22561,7 +22561,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="380" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>31</v>
       </c>
@@ -22630,7 +22630,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="381" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>31</v>
       </c>
@@ -22699,7 +22699,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="382" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>31</v>
       </c>
@@ -22772,7 +22772,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="383" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>31</v>
       </c>
@@ -22841,7 +22841,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="384" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>31</v>
       </c>
@@ -22867,7 +22867,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="385" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>31</v>
       </c>
@@ -22936,7 +22936,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="386" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>31</v>
       </c>
@@ -23005,7 +23005,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>31</v>
       </c>
@@ -23078,7 +23078,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="388" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>31</v>
       </c>
@@ -23147,7 +23147,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="389" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>31</v>
       </c>
@@ -23173,7 +23173,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="390" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>31</v>
       </c>
@@ -23242,7 +23242,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="391" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>31</v>
       </c>
@@ -23311,7 +23311,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>31</v>
       </c>
@@ -23384,7 +23384,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="393" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>31</v>
       </c>
@@ -23453,7 +23453,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="394" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>31</v>
       </c>
@@ -23479,7 +23479,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="395" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>31</v>
       </c>
@@ -23548,7 +23548,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="396" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>31</v>
       </c>
@@ -23617,7 +23617,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="397" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>31</v>
       </c>
@@ -23690,7 +23690,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="398" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>31</v>
       </c>
@@ -23759,7 +23759,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="399" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>35</v>
       </c>
@@ -23785,7 +23785,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="400" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>35</v>
       </c>
@@ -23854,7 +23854,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="401" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>35</v>
       </c>
@@ -23923,7 +23923,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="402" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>35</v>
       </c>
@@ -23996,7 +23996,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="403" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>35</v>
       </c>
@@ -24065,7 +24065,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="404" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>35</v>
       </c>
@@ -24091,7 +24091,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="405" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>35</v>
       </c>
@@ -24160,7 +24160,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>35</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>35</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="408" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>35</v>
       </c>
@@ -24371,7 +24371,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="409" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>35</v>
       </c>
@@ -24397,7 +24397,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="410" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>35</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="411" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>35</v>
       </c>
@@ -24535,7 +24535,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="412" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>35</v>
       </c>
@@ -24608,7 +24608,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="413" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>35</v>
       </c>
@@ -24677,7 +24677,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="414" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>35</v>
       </c>
@@ -24703,7 +24703,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="415" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>35</v>
       </c>
@@ -24772,7 +24772,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="416" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>35</v>
       </c>
@@ -24841,7 +24841,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>35</v>
       </c>
@@ -24914,7 +24914,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="418" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>35</v>
       </c>
@@ -24983,7 +24983,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="419" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>35</v>
       </c>
@@ -25009,7 +25009,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="420" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>35</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="421" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>35</v>
       </c>
@@ -25147,7 +25147,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="422" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>35</v>
       </c>
@@ -25220,7 +25220,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="423" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>35</v>
       </c>
@@ -25289,7 +25289,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="424" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>35</v>
       </c>
@@ -25315,7 +25315,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="425" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>35</v>
       </c>
@@ -25384,7 +25384,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="426" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>35</v>
       </c>
@@ -25453,7 +25453,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="427" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>35</v>
       </c>
@@ -25526,7 +25526,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="428" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>35</v>
       </c>
@@ -25595,7 +25595,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="429" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>37</v>
       </c>
@@ -25621,7 +25621,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="430" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>37</v>
       </c>
@@ -25690,7 +25690,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="431" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>37</v>
       </c>
@@ -25759,7 +25759,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="432" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>37</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="433" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>37</v>
       </c>
@@ -25901,7 +25901,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="434" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>37</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="435" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>37</v>
       </c>
@@ -25996,7 +25996,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="436" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>37</v>
       </c>
@@ -26065,7 +26065,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="437" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>37</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="438" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>37</v>
       </c>
@@ -26207,7 +26207,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="439" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>37</v>
       </c>
@@ -26233,7 +26233,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="440" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>37</v>
       </c>
@@ -26302,7 +26302,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="441" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>37</v>
       </c>
@@ -26371,7 +26371,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>37</v>
       </c>
@@ -26444,7 +26444,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="443" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>37</v>
       </c>
@@ -26513,7 +26513,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="444" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>40</v>
       </c>
@@ -26539,7 +26539,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="445" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>40</v>
       </c>
@@ -26608,7 +26608,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="446" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>40</v>
       </c>
@@ -26677,7 +26677,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="447" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>40</v>
       </c>
@@ -26750,7 +26750,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="448" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>40</v>
       </c>
@@ -26819,7 +26819,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="449" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>40</v>
       </c>
@@ -26845,7 +26845,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="450" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>40</v>
       </c>
@@ -26914,7 +26914,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="451" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>40</v>
       </c>
@@ -26983,7 +26983,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>40</v>
       </c>
@@ -27056,7 +27056,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="453" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>40</v>
       </c>
@@ -27125,7 +27125,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="454" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>178</v>
       </c>
@@ -27151,7 +27151,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="455" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>178</v>
       </c>
@@ -27220,7 +27220,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="456" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>178</v>
       </c>
@@ -27289,7 +27289,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>178</v>
       </c>
@@ -27358,7 +27358,7 @@
         <v>92227251.175370395</v>
       </c>
     </row>
-    <row r="458" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>178</v>
       </c>
